--- a/app/development/catalogo/data/catalogo_codigos_defeitos.xlsx
+++ b/app/development/catalogo/data/catalogo_codigos_defeitos.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Plan1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Plan1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="294">
   <si>
     <t xml:space="preserve">CÓDIGO DA FALHA</t>
   </si>
@@ -79,13 +79,13 @@
     <t xml:space="preserve">A9</t>
   </si>
   <si>
-    <t xml:space="preserve">Sem audio no Tweteer</t>
+    <t xml:space="preserve">Sem áudio no Tweteer</t>
   </si>
   <si>
     <t xml:space="preserve">A10</t>
   </si>
   <si>
-    <t xml:space="preserve">Sem audio no alto falante</t>
+    <t xml:space="preserve">Sem áudio no alto falante</t>
   </si>
   <si>
     <t xml:space="preserve">A11</t>
@@ -97,13 +97,13 @@
     <t xml:space="preserve">A12</t>
   </si>
   <si>
-    <t xml:space="preserve">Volume minimo não atua</t>
+    <t xml:space="preserve">Volume mínimo não atua</t>
   </si>
   <si>
     <t xml:space="preserve">A13</t>
   </si>
   <si>
-    <t xml:space="preserve">Audio Baixo</t>
+    <t xml:space="preserve">Áudio Baixo</t>
   </si>
   <si>
     <t xml:space="preserve">A14</t>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">G4</t>
   </si>
   <si>
-    <t xml:space="preserve">Loader com ruidos</t>
+    <t xml:space="preserve">Loader com ruídos</t>
   </si>
   <si>
     <t xml:space="preserve">GB</t>
@@ -253,7 +253,7 @@
     <t xml:space="preserve">HP3</t>
   </si>
   <si>
-    <t xml:space="preserve">Audio Oscilando</t>
+    <t xml:space="preserve">Áudio Oscilando</t>
   </si>
   <si>
     <t xml:space="preserve">HP4</t>
@@ -265,7 +265,7 @@
     <t xml:space="preserve">HP5</t>
   </si>
   <si>
-    <t xml:space="preserve">Repertições de ECO</t>
+    <t xml:space="preserve">Repetições de ECO</t>
   </si>
   <si>
     <t xml:space="preserve">HP6</t>
@@ -373,7 +373,7 @@
     <t xml:space="preserve">LD9</t>
   </si>
   <si>
-    <t xml:space="preserve">Excesso de Digitos</t>
+    <t xml:space="preserve">Excesso de Dígitos</t>
   </si>
   <si>
     <t xml:space="preserve">LD10</t>
@@ -685,7 +685,7 @@
     <t xml:space="preserve">T6</t>
   </si>
   <si>
-    <t xml:space="preserve">Volume maximo não atua</t>
+    <t xml:space="preserve">Volume máximo não atua</t>
   </si>
   <si>
     <t xml:space="preserve">T7</t>
@@ -829,13 +829,13 @@
     <t xml:space="preserve">PM1</t>
   </si>
   <si>
-    <t xml:space="preserve">Potencia Maxima</t>
+    <t xml:space="preserve">Potencia Máxima</t>
   </si>
   <si>
     <t xml:space="preserve">PM2</t>
   </si>
   <si>
-    <t xml:space="preserve">Potencia Minima</t>
+    <t xml:space="preserve">Potencia Mínima</t>
   </si>
   <si>
     <t xml:space="preserve">CTT</t>
@@ -868,9 +868,6 @@
     <t xml:space="preserve">BP1</t>
   </si>
   <si>
-    <t xml:space="preserve">Buzer não Atua</t>
-  </si>
-  <si>
     <t xml:space="preserve">FF</t>
   </si>
   <si>
@@ -898,13 +895,13 @@
     <t xml:space="preserve">ALT</t>
   </si>
   <si>
-    <t xml:space="preserve">ALETA NÃO ABRE/FECHA</t>
+    <t xml:space="preserve">Aleta não abre/fecha</t>
   </si>
   <si>
     <t xml:space="preserve">A15</t>
   </si>
   <si>
-    <t xml:space="preserve">RUIDO NA HÉLICE</t>
+    <t xml:space="preserve">Ruído na Hélice</t>
   </si>
 </sst>
 </file>
@@ -1001,121 +998,15 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.25"/>
   </cols>
   <sheetData>
@@ -2268,55 +2159,55 @@
         <v>281</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>282</v>
+        <v>45</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
